--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>Key</t>
   </si>
@@ -45,27 +45,6 @@
   </si>
   <si>
     <t>Possibility</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>Elite</t>
-  </si>
-  <si>
-    <t>精英</t>
-  </si>
-  <si>
-    <t>Sanctuary</t>
-  </si>
-  <si>
-    <t>庇护所</t>
-  </si>
-  <si>
-    <t>Soul Spring</t>
-  </si>
-  <si>
-    <t>灵魂之泉</t>
   </si>
   <si>
     <t>Minion</t>
@@ -1117,7 +1096,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="27.5454545454545" customWidth="1"/>
@@ -1158,93 +1137,93 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-2</v>
+      </c>
+      <c r="F2">
         <v>1</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>-1</v>
+      </c>
+      <c r="F4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>1</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1252,19 +1231,19 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0.5</v>
@@ -1272,221 +1251,141 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
         <v>1</v>
-      </c>
-      <c r="F11">
-        <v>0.5</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>0.66</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>3</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-      <c r="F17">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-      <c r="F18">
         <v>0.5</v>
       </c>
     </row>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="RougeMap" sheetId="1" r:id="rId1"/>
+    <sheet name="RougeFights" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="81">
   <si>
     <t>Key</t>
   </si>
@@ -123,19 +124,167 @@
   </si>
   <si>
     <t>邪恶熔炉</t>
+  </si>
+  <si>
+    <t>Enemies</t>
+  </si>
+  <si>
+    <t>GoldReward</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>["Clumsy Gunner", "Clumsy Gunner", "Clumsy Gunner"]</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>["Mountain Bandit Cluster", "Mountain Bandit Cluster", "Mountain Bandit Cluster", "Mountain Bandit Cluster"]</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>["Cultist"]</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>["Mercenary Warrior", "Mercenary Shield Guard"]</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>["Mercenary Soldier", "Mercenary Soldier", "Mercenary Shield Guard"]</t>
+  </si>
+  <si>
+    <t>1-6</t>
+  </si>
+  <si>
+    <t>["Mercenary Warrior", "Mercenary Employer"]</t>
+  </si>
+  <si>
+    <t>1-7</t>
+  </si>
+  <si>
+    <t>["Mercenary Soldier", "Mercenary Soldier", "Mercenary Employer"]</t>
+  </si>
+  <si>
+    <t>1-8</t>
+  </si>
+  <si>
+    <t>["Wolf Mother", "Wolf Cub", "Wolf Cub"]</t>
+  </si>
+  <si>
+    <t>1-9</t>
+  </si>
+  <si>
+    <t>["Wolf", "Wolf"]</t>
+  </si>
+  <si>
+    <t>1-10</t>
+  </si>
+  <si>
+    <t>["Crow"]</t>
+  </si>
+  <si>
+    <t>1-11</t>
+  </si>
+  <si>
+    <t>["Little Monkey", "Little Monkey", "Little Monkey"]</t>
+  </si>
+  <si>
+    <t>1-12</t>
+  </si>
+  <si>
+    <t>["Little Monkey", "Wolf Cub", "Wolf Cub"]</t>
+  </si>
+  <si>
+    <t>1-13</t>
+  </si>
+  <si>
+    <t>["White Wolf King"]</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>1-14</t>
+  </si>
+  <si>
+    <t>["Six Ear Macaque"]</t>
+  </si>
+  <si>
+    <t>1-15</t>
+  </si>
+  <si>
+    <t>["Two Headed Snake"]</t>
+  </si>
+  <si>
+    <t>1-16</t>
+  </si>
+  <si>
+    <t>["Bandit Leader", "Clumsy Gunner", "Clumsy Gunner", "Mountain Bandit Cluster", "Mountain Bandit Cluster"]</t>
+  </si>
+  <si>
+    <t>1-17</t>
+  </si>
+  <si>
+    <t>["Troll"]</t>
+  </si>
+  <si>
+    <t>1-18</t>
+  </si>
+  <si>
+    <t>["Bronze Guardian", "Bronze Imp", "Bronze Imp", "Bronze Imp"]</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>1-19</t>
+  </si>
+  <si>
+    <t>["Ancient Tree"]</t>
+  </si>
+  <si>
+    <t>1-20</t>
+  </si>
+  <si>
+    <t>["Formless Water", "Formless Water", "Formless Water", "Formless Water", "Formless Water"]</t>
+  </si>
+  <si>
+    <t>1-21</t>
+  </si>
+  <si>
+    <t>["Burning Avenger"]</t>
+  </si>
+  <si>
+    <t>1-22</t>
+  </si>
+  <si>
+    <t>["Earth Burier"]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +297,17 @@
       <sz val="9"/>
       <color theme="0"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -295,7 +455,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -306,6 +466,12 @@
       <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
       </patternFill>
     </fill>
     <fill>
@@ -645,137 +811,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -784,6 +950,36 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1394,4 +1590,413 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="116.109090909091" customWidth="1"/>
+    <col min="4" max="4" width="34.8909090909091" customWidth="1"/>
+    <col min="5" max="5" width="18.2727272727273" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="5">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="8">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="5">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="8">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="5">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="8">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="5">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="8">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="5">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="8">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="5">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="8">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="5">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="8">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="5">
+        <v>100</v>
+      </c>
+      <c r="E16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="8">
+        <v>100</v>
+      </c>
+      <c r="E17" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" s="5">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0</v>
+      </c>
+      <c r="E20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D22" s="5">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="8">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RougeMap" sheetId="1" r:id="rId1"/>
     <sheet name="RougeFights" sheetId="2" r:id="rId2"/>
+    <sheet name="RougeEvent" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="99">
   <si>
     <t>Key</t>
   </si>
@@ -231,7 +232,7 @@
     <t>1-16</t>
   </si>
   <si>
-    <t>["Bandit Leader", "Clumsy Gunner", "Clumsy Gunner", "Mountain Bandit Cluster", "Mountain Bandit Cluster"]</t>
+    <t>["Bandit Leader", "Clumsy Gunner", "Clumsy Gunner", "Mountain Bandit Cluster"]</t>
   </si>
   <si>
     <t>1-17</t>
@@ -258,7 +259,7 @@
     <t>1-20</t>
   </si>
   <si>
-    <t>["Formless Water", "Formless Water", "Formless Water", "Formless Water", "Formless Water"]</t>
+    <t>["Formless Water", "Formless Water", "Formless Water", "Formless Water"]</t>
   </si>
   <si>
     <t>1-21</t>
@@ -271,6 +272,60 @@
   </si>
   <si>
     <t>["Earth Burier"]</t>
+  </si>
+  <si>
+    <t>Options</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>["Hero1","Hero1","Hero3"]</t>
+  </si>
+  <si>
+    <t>选择英雄招募</t>
+  </si>
+  <si>
+    <t>SoulFountain</t>
+  </si>
+  <si>
+    <t>灵魂之泉</t>
+  </si>
+  <si>
+    <t>["Card1","Card2","Card3"]</t>
+  </si>
+  <si>
+    <t>选择遗物</t>
+  </si>
+  <si>
+    <t>SacredCemetery</t>
+  </si>
+  <si>
+    <t>["Relic1","Relic2","Relic3"]</t>
+  </si>
+  <si>
+    <t>选择卡牌</t>
+  </si>
+  <si>
+    <t>Treasure</t>
+  </si>
+  <si>
+    <t>宝箱</t>
+  </si>
+  <si>
+    <t>["宝箱"]</t>
+  </si>
+  <si>
+    <t>宝藏！</t>
+  </si>
+  <si>
+    <t>CurseFusion</t>
+  </si>
+  <si>
+    <t>["开始融合"]</t>
+  </si>
+  <si>
+    <t>融合你的英雄</t>
   </si>
 </sst>
 </file>
@@ -954,20 +1009,20 @@
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1627,10 +1682,10 @@
       <c r="B2" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>20</v>
       </c>
       <c r="E2" t="s">
@@ -1644,10 +1699,10 @@
       <c r="B3" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="6">
         <v>20</v>
       </c>
       <c r="E3" t="s">
@@ -1661,10 +1716,10 @@
       <c r="B4" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>20</v>
       </c>
       <c r="E4" t="s">
@@ -1678,10 +1733,10 @@
       <c r="B5" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <v>20</v>
       </c>
       <c r="E5" t="s">
@@ -1695,10 +1750,10 @@
       <c r="B6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>20</v>
       </c>
       <c r="E6" t="s">
@@ -1712,10 +1767,10 @@
       <c r="B7" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <v>20</v>
       </c>
       <c r="E7" t="s">
@@ -1729,10 +1784,10 @@
       <c r="B8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>20</v>
       </c>
       <c r="E8" t="s">
@@ -1746,10 +1801,10 @@
       <c r="B9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="6">
         <v>20</v>
       </c>
       <c r="E9" t="s">
@@ -1763,10 +1818,10 @@
       <c r="B10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>20</v>
       </c>
       <c r="E10" t="s">
@@ -1780,10 +1835,10 @@
       <c r="B11" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="6">
         <v>20</v>
       </c>
       <c r="E11" t="s">
@@ -1797,10 +1852,10 @@
       <c r="B12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>20</v>
       </c>
       <c r="E12" t="s">
@@ -1814,10 +1869,10 @@
       <c r="B13" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="6">
         <v>20</v>
       </c>
       <c r="E13" t="s">
@@ -1831,10 +1886,10 @@
       <c r="B14" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>100</v>
       </c>
       <c r="E14" t="s">
@@ -1848,10 +1903,10 @@
       <c r="B15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="6">
         <v>100</v>
       </c>
       <c r="E15" t="s">
@@ -1865,10 +1920,10 @@
       <c r="B16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>100</v>
       </c>
       <c r="E16" t="s">
@@ -1882,10 +1937,10 @@
       <c r="B17" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="6">
         <v>100</v>
       </c>
       <c r="E17" t="s">
@@ -1899,10 +1954,10 @@
       <c r="B18" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>100</v>
       </c>
       <c r="E18" t="s">
@@ -1916,10 +1971,10 @@
       <c r="B19" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="6">
         <v>0</v>
       </c>
       <c r="E19" t="s">
@@ -1933,10 +1988,10 @@
       <c r="B20" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>0</v>
       </c>
       <c r="E20" t="s">
@@ -1950,10 +2005,10 @@
       <c r="B21" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="6">
         <v>0</v>
       </c>
       <c r="E21" t="s">
@@ -1967,10 +2022,10 @@
       <c r="B22" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>0</v>
       </c>
       <c r="E22" t="s">
@@ -1984,10 +2039,10 @@
       <c r="B23" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="6">
         <v>0</v>
       </c>
       <c r="E23" t="s">
@@ -1999,4 +2054,125 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="21.9090909090909" customWidth="1"/>
+    <col min="2" max="2" width="28.5454545454545" customWidth="1"/>
+    <col min="3" max="3" width="57.0909090909091" customWidth="1"/>
+    <col min="4" max="4" width="37" customWidth="1"/>
+    <col min="5" max="5" width="19.7272727272727" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="RougeMap" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="91">
   <si>
     <t>Key</t>
   </si>
@@ -136,18 +136,6 @@
     <t>Type</t>
   </si>
   <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>["Clumsy Gunner", "Clumsy Gunner", "Clumsy Gunner"]</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>["Mountain Bandit Cluster", "Mountain Bandit Cluster", "Mountain Bandit Cluster", "Mountain Bandit Cluster"]</t>
-  </si>
-  <si>
     <t>1-3</t>
   </si>
   <si>
@@ -232,7 +220,7 @@
     <t>1-16</t>
   </si>
   <si>
-    <t>["Bandit Leader", "Clumsy Gunner", "Clumsy Gunner", "Mountain Bandit Cluster"]</t>
+    <t>["Bandit Leader", "Crow"]</t>
   </si>
   <si>
     <t>1-17</t>
@@ -241,25 +229,13 @@
     <t>["Troll"]</t>
   </si>
   <si>
-    <t>1-18</t>
-  </si>
-  <si>
-    <t>["Bronze Guardian", "Bronze Imp", "Bronze Imp", "Bronze Imp"]</t>
+    <t>1-20</t>
+  </si>
+  <si>
+    <t>["Formless Water", "Formless Water", "Formless Water", "Formless Water"]</t>
   </si>
   <si>
     <t>Boss</t>
-  </si>
-  <si>
-    <t>1-19</t>
-  </si>
-  <si>
-    <t>["Ancient Tree"]</t>
-  </si>
-  <si>
-    <t>1-20</t>
-  </si>
-  <si>
-    <t>["Formless Water", "Formless Water", "Formless Water", "Formless Water"]</t>
   </si>
   <si>
     <t>1-21</t>
@@ -1650,7 +1626,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="116.109090909091" customWidth="1"/>
@@ -1856,44 +1832,44 @@
         <v>56</v>
       </c>
       <c r="D12" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="6">
+        <v>100</v>
+      </c>
+      <c r="E13" t="s">
         <v>57</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="6">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" s="4">
         <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1910,7 +1886,7 @@
         <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -1927,7 +1903,7 @@
         <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1941,112 +1917,44 @@
         <v>67</v>
       </c>
       <c r="D17" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
         <v>68</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="4">
-        <v>100</v>
-      </c>
-      <c r="E18" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D19" s="6">
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="4">
-        <v>0</v>
-      </c>
-      <c r="E20" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D21" s="6">
-        <v>0</v>
-      </c>
-      <c r="E21" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="4">
-        <v>0</v>
-      </c>
-      <c r="E22" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="6">
-        <v>0</v>
-      </c>
-      <c r="E23" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2080,10 +1988,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2097,78 +2005,78 @@
         <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
       </c>
       <c r="D6" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RougeMap" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="91">
   <si>
     <t>Key</t>
   </si>
@@ -184,18 +184,6 @@
     <t>["Crow"]</t>
   </si>
   <si>
-    <t>1-11</t>
-  </si>
-  <si>
-    <t>["Little Monkey", "Little Monkey", "Little Monkey"]</t>
-  </si>
-  <si>
-    <t>1-12</t>
-  </si>
-  <si>
-    <t>["Little Monkey", "Wolf Cub", "Wolf Cub"]</t>
-  </si>
-  <si>
     <t>1-13</t>
   </si>
   <si>
@@ -302,6 +290,18 @@
   </si>
   <si>
     <t>融合你的英雄</t>
+  </si>
+  <si>
+    <t>Shelter</t>
+  </si>
+  <si>
+    <t>庇护所</t>
+  </si>
+  <si>
+    <t>["休息"]</t>
+  </si>
+  <si>
+    <t>在此地休息，为所有英雄回复体力</t>
   </si>
 </sst>
 </file>
@@ -1626,7 +1626,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="116.109090909091" customWidth="1"/>
@@ -1798,44 +1798,44 @@
         <v>52</v>
       </c>
       <c r="D10" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="6">
+        <v>100</v>
+      </c>
+      <c r="E11" t="s">
         <v>53</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="6">
-        <v>20</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4">
         <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -1852,7 +1852,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -1869,7 +1869,7 @@
         <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -1883,78 +1883,44 @@
         <v>63</v>
       </c>
       <c r="D15" s="6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
         <v>64</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D16" s="4">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" s="6">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="4">
-        <v>0</v>
-      </c>
-      <c r="E18" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0</v>
-      </c>
-      <c r="E19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1967,14 +1933,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="21.9090909090909" customWidth="1"/>
     <col min="2" max="2" width="28.5454545454545" customWidth="1"/>
     <col min="3" max="3" width="57.0909090909091" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="19.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="35.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1988,10 +1954,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2005,77 +1971,94 @@
         <v>25</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
         <v>29</v>
       </c>
       <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
         <v>89</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>90</v>
       </c>
     </row>

--- a/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
+++ b/Src/Assets/StreamingAssets/Common/Tables/Tables/RougeMap.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="RougeMap" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
     <t>["Hero1","Hero1","Hero3"]</t>
   </si>
   <si>
-    <t>选择英雄招募</t>
+    <t>你来到了热闹的酒馆，这里有各路英雄等你来招募</t>
   </si>
   <si>
     <t>SoulFountain</t>
@@ -259,7 +259,7 @@
     <t>["Card1","Card2","Card3"]</t>
   </si>
   <si>
-    <t>选择遗物</t>
+    <t>你发现了一处灵魂之泉，泉水旁浮现出强力卡牌，快来挑选。</t>
   </si>
   <si>
     <t>SacredCemetery</t>
@@ -268,7 +268,7 @@
     <t>["Relic1","Relic2","Relic3"]</t>
   </si>
   <si>
-    <t>选择卡牌</t>
+    <t>你来到神圣墓地，这里藏着不少神秘遗物，选一件带走吧。</t>
   </si>
   <si>
     <t>Treasure</t>
@@ -277,19 +277,19 @@
     <t>宝箱</t>
   </si>
   <si>
-    <t>["宝箱"]</t>
-  </si>
-  <si>
-    <t>宝藏！</t>
+    <t>["打开宝箱"]</t>
+  </si>
+  <si>
+    <t>你发现了一个闪闪发光的宝箱，打开就能获得丰厚宝藏。</t>
   </si>
   <si>
     <t>CurseFusion</t>
   </si>
   <si>
-    <t>["开始融合"]</t>
-  </si>
-  <si>
-    <t>融合你的英雄</t>
+    <t>["启动祭坛"]</t>
+  </si>
+  <si>
+    <t>你找到了看似被诅咒的祭坛，可以在这里融合英雄，但是代价是？</t>
   </si>
   <si>
     <t>Shelter</t>
@@ -1324,16 +1324,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.5454545454545" customWidth="1"/>
-    <col min="2" max="2" width="18.6545454545455" customWidth="1"/>
-    <col min="3" max="3" width="22.2727272727273" customWidth="1"/>
-    <col min="4" max="4" width="16.8181818181818" customWidth="1"/>
-    <col min="6" max="6" width="12.3545454545455" customWidth="1"/>
+    <col min="1" max="1" width="27.5416666666667" customWidth="1"/>
+    <col min="2" max="2" width="18.6583333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.275" customWidth="1"/>
+    <col min="4" max="4" width="16.8166666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.3583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" ht="14.25" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1627,14 +1627,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="3" max="3" width="116.109090909091" customWidth="1"/>
-    <col min="4" max="4" width="34.8909090909091" customWidth="1"/>
-    <col min="5" max="5" width="18.2727272727273" customWidth="1"/>
+    <col min="3" max="3" width="116.108333333333" customWidth="1"/>
+    <col min="4" max="4" width="34.8916666666667" customWidth="1"/>
+    <col min="5" max="5" width="18.275" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="14.25" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1651,7 +1651,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="14.25" spans="1:5">
       <c r="A2" s="9" t="s">
         <v>35</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" ht="14.25" spans="1:5">
       <c r="A3" s="11" t="s">
         <v>37</v>
       </c>
@@ -1685,7 +1685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" ht="14.25" spans="1:5">
       <c r="A4" s="9" t="s">
         <v>39</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" ht="14.25" spans="1:5">
       <c r="A5" s="11" t="s">
         <v>41</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" ht="14.25" spans="1:5">
       <c r="A6" s="9" t="s">
         <v>43</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" ht="14.25" spans="1:5">
       <c r="A7" s="11" t="s">
         <v>45</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" ht="14.25" spans="1:5">
       <c r="A8" s="9" t="s">
         <v>47</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" ht="14.25" spans="1:5">
       <c r="A9" s="11" t="s">
         <v>49</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" ht="14.25" spans="1:5">
       <c r="A10" s="9" t="s">
         <v>51</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" ht="14.25" spans="1:5">
       <c r="A11" s="11" t="s">
         <v>54</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" ht="14.25" spans="1:5">
       <c r="A12" s="9" t="s">
         <v>56</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" ht="14.25" spans="1:5">
       <c r="A13" s="11" t="s">
         <v>58</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" ht="14.25" spans="1:5">
       <c r="A14" s="9" t="s">
         <v>60</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" ht="14.25" spans="1:5">
       <c r="A15" s="11" t="s">
         <v>62</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" ht="14.25" spans="1:5">
       <c r="A16" s="9" t="s">
         <v>65</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" ht="14.25" spans="1:5">
       <c r="A17" s="11" t="s">
         <v>67</v>
       </c>
@@ -1934,16 +1934,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.9090909090909" customWidth="1"/>
-    <col min="2" max="2" width="28.5454545454545" customWidth="1"/>
-    <col min="3" max="3" width="57.0909090909091" customWidth="1"/>
+    <col min="1" max="1" width="21.9083333333333" customWidth="1"/>
+    <col min="2" max="2" width="28.5416666666667" customWidth="1"/>
+    <col min="3" max="3" width="57.0916666666667" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
-    <col min="5" max="5" width="35.6363636363636" customWidth="1"/>
+    <col min="5" max="5" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" ht="14.25" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" ht="14.25" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>24</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" ht="14.25" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>73</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" ht="14.25" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>77</v>
       </c>
